--- a/result_ent_2.xlsx
+++ b/result_ent_2.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25028"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5071419-DD26-4C6B-935E-643C6E384AC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="72">
   <si>
     <t>ФИО</t>
   </si>
@@ -45,114 +39,18 @@
     <t>История_Казахстана</t>
   </si>
   <si>
-    <t>Алиханов А.</t>
-  </si>
-  <si>
     <t>11-А</t>
   </si>
   <si>
     <t>Ж</t>
   </si>
   <si>
-    <t>Болатова Д.</t>
-  </si>
-  <si>
     <t>М</t>
   </si>
   <si>
-    <t>Ермеков М.</t>
-  </si>
-  <si>
     <t>Достижение</t>
   </si>
   <si>
-    <t>Искакова М.</t>
-  </si>
-  <si>
-    <t>Каримов Н.</t>
-  </si>
-  <si>
-    <t>Муратова З.</t>
-  </si>
-  <si>
-    <t>Нурахметов Б.</t>
-  </si>
-  <si>
-    <t>Оспанов Т.</t>
-  </si>
-  <si>
-    <t>Серикова М.</t>
-  </si>
-  <si>
-    <t>Утепов Д.</t>
-  </si>
-  <si>
-    <t>Ахметов Е.</t>
-  </si>
-  <si>
-    <t>Бауыржанова А.</t>
-  </si>
-  <si>
-    <t>Ганиұлы Р.</t>
-  </si>
-  <si>
-    <t>Даулетова А.</t>
-  </si>
-  <si>
-    <t>Жұмабай Н.</t>
-  </si>
-  <si>
-    <t>Ибрагимов К.</t>
-  </si>
-  <si>
-    <t>Касымова Д.</t>
-  </si>
-  <si>
-    <t>Маратов А.</t>
-  </si>
-  <si>
-    <t>Садыков Т.</t>
-  </si>
-  <si>
-    <t>Тлеулин Б.</t>
-  </si>
-  <si>
-    <t>Аманжол С.</t>
-  </si>
-  <si>
-    <t>Бексұлтан А.</t>
-  </si>
-  <si>
-    <t>Валиева Э.</t>
-  </si>
-  <si>
-    <t>Досмагамбетов М.</t>
-  </si>
-  <si>
-    <t>Есенгельдиева Ж.</t>
-  </si>
-  <si>
-    <t>Канатов Д.</t>
-  </si>
-  <si>
-    <t>Нурланов А.</t>
-  </si>
-  <si>
-    <t>Русланова М.</t>
-  </si>
-  <si>
-    <t>Султанов Т.</t>
-  </si>
-  <si>
-    <t>Хасенов Н.</t>
-  </si>
-  <si>
-    <t>11-Б</t>
-  </si>
-  <si>
-    <t>11-В</t>
-  </si>
-  <si>
     <t>Үздік аттестат</t>
   </si>
   <si>
@@ -190,12 +88,159 @@
   </si>
   <si>
     <t>Дата</t>
+  </si>
+  <si>
+    <t>Абзал Ерасыл</t>
+  </si>
+  <si>
+    <t>АЙТМАҒАМБЕТ НҰРАЙ</t>
+  </si>
+  <si>
+    <t>АЙТУАР НҰРХАН</t>
+  </si>
+  <si>
+    <t>АХАТОВА ЭЛЬНУРА</t>
+  </si>
+  <si>
+    <t>АХМЕТОВА ЗИНИРА</t>
+  </si>
+  <si>
+    <t>ӘЛІБЕК ӘЛИ</t>
+  </si>
+  <si>
+    <t>Болат Асанәлі</t>
+  </si>
+  <si>
+    <t>БОРАНБАЕВА ЯСМИН</t>
+  </si>
+  <si>
+    <t>Габдуллин Жандос</t>
+  </si>
+  <si>
+    <t>Жамбаев Ерасыл</t>
+  </si>
+  <si>
+    <t>Жанас Ерасыл</t>
+  </si>
+  <si>
+    <t>ЖҰМАБАЙ АЗИЗ</t>
+  </si>
+  <si>
+    <t>Жұмкеш Айдана</t>
+  </si>
+  <si>
+    <t>Иран Аружан</t>
+  </si>
+  <si>
+    <t>Кабыкенова Айсана</t>
+  </si>
+  <si>
+    <t>Капаров Жаксылык</t>
+  </si>
+  <si>
+    <t>ҚАБДУ ӘБІЛМАНСҰР</t>
+  </si>
+  <si>
+    <t>ҚАБДЫЛМЕН ЕЛДАНА</t>
+  </si>
+  <si>
+    <t>ҚАИРБЕК НҰРАЙ</t>
+  </si>
+  <si>
+    <t>МЕДІҒАТ КӘУСАР</t>
+  </si>
+  <si>
+    <t>НУГМАНОВА АРУНА</t>
+  </si>
+  <si>
+    <t>Нұрсеит Дилара</t>
+  </si>
+  <si>
+    <t>Нұрхан Айнұр</t>
+  </si>
+  <si>
+    <t>САРЫБАЙ ЖАНЕРКЕ</t>
+  </si>
+  <si>
+    <t>Хасеин Нұрхан</t>
+  </si>
+  <si>
+    <t>Ақан Әділ</t>
+  </si>
+  <si>
+    <t>АМАНГЕЛДІ МЕРЕЙ</t>
+  </si>
+  <si>
+    <t>Арманқызы Томирис</t>
+  </si>
+  <si>
+    <t>АУБАКИРОВА КАМИЛА</t>
+  </si>
+  <si>
+    <t>ӘНУАРБЕК ӘДЕМІ</t>
+  </si>
+  <si>
+    <t>БАЖЕНОВА ДАЙАНА</t>
+  </si>
+  <si>
+    <t>Бақытжан Аружан</t>
+  </si>
+  <si>
+    <t>БАЛТАБЕК НҰРХАН</t>
+  </si>
+  <si>
+    <t>ДАУТОВА ФАРИЗА</t>
+  </si>
+  <si>
+    <t>ЖАКУПОВА ДАЯНА</t>
+  </si>
+  <si>
+    <t>ЖАНТЕМИРОВА КАМИЛА</t>
+  </si>
+  <si>
+    <t>ЖҰМАН ДАНА</t>
+  </si>
+  <si>
+    <t>Кенин Мансур</t>
+  </si>
+  <si>
+    <t>КСЕМБАЕВА АЙЗАРА</t>
+  </si>
+  <si>
+    <t>ҚАБЫЛБЕК ІҢКӘР</t>
+  </si>
+  <si>
+    <t>НУРГАЛИЕВА ИНКАР</t>
+  </si>
+  <si>
+    <t>НУРУМОВА АДИНА</t>
+  </si>
+  <si>
+    <t>САРСЕНБАЕВА АДИЯ</t>
+  </si>
+  <si>
+    <t>САТТАРОВА АЙЗАРА</t>
+  </si>
+  <si>
+    <t>СЕЙТМУХАМЕТ РАМИНА</t>
+  </si>
+  <si>
+    <t>ТАБАЕВА ДИЛЯРА</t>
+  </si>
+  <si>
+    <t>ТЕКЕНОВА НАЗЫМ</t>
+  </si>
+  <si>
+    <t>ШАЙМАН АҚЕРКЕ</t>
+  </si>
+  <si>
+    <t>11-Ә</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -539,15 +584,15 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K53"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
@@ -561,7 +606,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -582,16 +627,16 @@
         <v>5</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -599,13 +644,13 @@
         <v>46123</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E2" s="6">
         <v>9</v>
@@ -617,7 +662,7 @@
         <v>4</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="I2" s="6">
         <v>32</v>
@@ -632,13 +677,13 @@
         <v>46123</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" s="6">
         <v>9</v>
@@ -650,7 +695,7 @@
         <v>16</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="I3" s="6">
         <v>43</v>
@@ -665,13 +710,13 @@
         <v>46123</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E4" s="6">
         <v>8</v>
@@ -683,7 +728,7 @@
         <v>17</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="I4" s="6">
         <v>35</v>
@@ -698,13 +743,13 @@
         <v>46123</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" s="6">
         <v>8</v>
@@ -716,7 +761,7 @@
         <v>16</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="I5" s="6">
         <v>49</v>
@@ -731,13 +776,13 @@
         <v>46123</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E6" s="6">
         <v>9</v>
@@ -749,7 +794,7 @@
         <v>20</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="I6" s="6">
         <v>48</v>
@@ -758,7 +803,7 @@
         <v>40</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -766,10 +811,10 @@
         <v>46123</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>8</v>
@@ -784,7 +829,7 @@
         <v>18</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="I7" s="6">
         <v>49</v>
@@ -793,7 +838,7 @@
         <v>49</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -801,13 +846,13 @@
         <v>46123</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E8" s="6">
         <v>8</v>
@@ -819,7 +864,7 @@
         <v>18</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="I8" s="6">
         <v>46</v>
@@ -828,7 +873,7 @@
         <v>37</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -836,13 +881,13 @@
         <v>46123</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E9" s="6">
         <v>9</v>
@@ -854,7 +899,7 @@
         <v>20</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="I9" s="6">
         <v>32</v>
@@ -869,25 +914,25 @@
         <v>46123</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="6">
+        <v>9</v>
+      </c>
+      <c r="F10" s="6">
+        <v>9</v>
+      </c>
+      <c r="G10" s="6">
+        <v>9</v>
+      </c>
+      <c r="H10" s="6" t="s">
         <v>18</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="6">
-        <v>9</v>
-      </c>
-      <c r="F10" s="6">
-        <v>9</v>
-      </c>
-      <c r="G10" s="6">
-        <v>9</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>50</v>
       </c>
       <c r="I10" s="6">
         <v>42</v>
@@ -902,13 +947,13 @@
         <v>46123</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E11" s="6">
         <v>8</v>
@@ -920,7 +965,7 @@
         <v>12</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="I11" s="6">
         <v>39</v>
@@ -935,13 +980,13 @@
         <v>46123</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E12" s="6">
         <v>9</v>
@@ -953,7 +998,7 @@
         <v>19</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="I12" s="6">
         <v>43</v>
@@ -968,10 +1013,10 @@
         <v>46123</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>8</v>
@@ -986,7 +1031,7 @@
         <v>14</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="I13" s="6">
         <v>43</v>
@@ -995,7 +1040,7 @@
         <v>49</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1003,13 +1048,13 @@
         <v>46123</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E14" s="6">
         <v>8</v>
@@ -1021,7 +1066,7 @@
         <v>18</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="I14" s="6">
         <v>47</v>
@@ -1030,7 +1075,7 @@
         <v>45</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1038,13 +1083,13 @@
         <v>46123</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E15" s="6">
         <v>10</v>
@@ -1056,7 +1101,7 @@
         <v>16</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="I15" s="6">
         <v>43</v>
@@ -1065,7 +1110,7 @@
         <v>45</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1073,13 +1118,13 @@
         <v>46123</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E16" s="6">
         <v>8</v>
@@ -1091,7 +1136,7 @@
         <v>17</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="I16" s="6">
         <v>33</v>
@@ -1106,13 +1151,13 @@
         <v>46123</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E17" s="6">
         <v>6</v>
@@ -1124,7 +1169,7 @@
         <v>9</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="I17" s="6">
         <v>38</v>
@@ -1139,10 +1184,10 @@
         <v>46123</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>8</v>
@@ -1157,7 +1202,7 @@
         <v>13</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="I18" s="6">
         <v>32</v>
@@ -1172,13 +1217,13 @@
         <v>46123</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E19" s="6">
         <v>8</v>
@@ -1190,7 +1235,7 @@
         <v>13</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="I19" s="6">
         <v>35</v>
@@ -1205,13 +1250,13 @@
         <v>46123</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E20" s="6">
         <v>9</v>
@@ -1223,7 +1268,7 @@
         <v>14</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="I20" s="6">
         <v>37</v>
@@ -1238,13 +1283,13 @@
         <v>46123</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E21" s="6">
         <v>10</v>
@@ -1256,7 +1301,7 @@
         <v>20</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="I21" s="6">
         <v>49</v>
@@ -1265,7 +1310,7 @@
         <v>40</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -1273,13 +1318,13 @@
         <v>46123</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E22" s="6">
         <v>9</v>
@@ -1291,7 +1336,7 @@
         <v>13</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="I22" s="6">
         <v>32</v>
@@ -1306,13 +1351,13 @@
         <v>46123</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E23" s="6">
         <v>8</v>
@@ -1324,7 +1369,7 @@
         <v>14</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="I23" s="6">
         <v>40</v>
@@ -1339,13 +1384,13 @@
         <v>46123</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E24" s="6">
         <v>9</v>
@@ -1357,7 +1402,7 @@
         <v>12</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="I24" s="6">
         <v>42</v>
@@ -1372,13 +1417,13 @@
         <v>46123</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E25" s="6">
         <v>6</v>
@@ -1390,7 +1435,7 @@
         <v>12</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="I25" s="6">
         <v>42</v>
@@ -1405,10 +1450,10 @@
         <v>46123</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>8</v>
@@ -1423,7 +1468,7 @@
         <v>9</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="I26" s="6">
         <v>32</v>
@@ -1438,13 +1483,13 @@
         <v>46123</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E27" s="6">
         <v>6</v>
@@ -1456,7 +1501,7 @@
         <v>15</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="I27" s="6">
         <v>33</v>
@@ -1471,13 +1516,13 @@
         <v>46123</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E28" s="6">
         <v>10</v>
@@ -1489,7 +1534,7 @@
         <v>18</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="I28" s="6">
         <v>42</v>
@@ -1504,13 +1549,13 @@
         <v>46123</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E29" s="6">
         <v>9</v>
@@ -1522,7 +1567,7 @@
         <v>20</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="I29" s="6">
         <v>45</v>
@@ -1531,7 +1576,7 @@
         <v>48</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1539,13 +1584,13 @@
         <v>46123</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E30" s="6">
         <v>9</v>
@@ -1557,7 +1602,7 @@
         <v>12</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="I30" s="6">
         <v>33</v>
@@ -1572,13 +1617,13 @@
         <v>46123</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E31" s="6">
         <v>8</v>
@@ -1590,7 +1635,7 @@
         <v>19</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="I31" s="6">
         <v>45</v>
@@ -1601,290 +1646,635 @@
       <c r="K31" s="5"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="10"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="6"/>
+      <c r="A32" s="11">
+        <v>46123</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E32" s="6">
+        <v>9</v>
+      </c>
+      <c r="F32" s="6">
+        <v>9</v>
+      </c>
+      <c r="G32" s="6">
+        <v>13</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I32" s="6">
+        <v>32</v>
+      </c>
+      <c r="J32" s="6">
+        <v>41</v>
+      </c>
       <c r="K32" s="5"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="10"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
+      <c r="A33" s="11">
+        <v>46123</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E33" s="6">
+        <v>8</v>
+      </c>
+      <c r="F33" s="6">
+        <v>7</v>
+      </c>
+      <c r="G33" s="6">
+        <v>14</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I33" s="6">
+        <v>40</v>
+      </c>
+      <c r="J33" s="6">
+        <v>47</v>
+      </c>
       <c r="K33" s="5"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="10"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="6"/>
+      <c r="A34" s="11">
+        <v>46123</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E34" s="6">
+        <v>9</v>
+      </c>
+      <c r="F34" s="6">
+        <v>9</v>
+      </c>
+      <c r="G34" s="6">
+        <v>12</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I34" s="6">
+        <v>42</v>
+      </c>
+      <c r="J34" s="6">
+        <v>32</v>
+      </c>
       <c r="K34" s="5"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="10"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
+      <c r="A35" s="11">
+        <v>46123</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E35" s="6">
+        <v>6</v>
+      </c>
+      <c r="F35" s="6">
+        <v>10</v>
+      </c>
+      <c r="G35" s="6">
+        <v>12</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I35" s="6">
+        <v>42</v>
+      </c>
+      <c r="J35" s="6">
+        <v>42</v>
+      </c>
       <c r="K35" s="5"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="10"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="6"/>
+      <c r="A36" s="11">
+        <v>46123</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E36" s="6">
+        <v>7</v>
+      </c>
+      <c r="F36" s="6">
+        <v>9</v>
+      </c>
+      <c r="G36" s="6">
+        <v>9</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" s="6">
+        <v>32</v>
+      </c>
+      <c r="J36" s="6">
+        <v>39</v>
+      </c>
       <c r="K36" s="5"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="10"/>
-      <c r="B37" s="3"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="6"/>
+      <c r="A37" s="11">
+        <v>46123</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E37" s="6">
+        <v>6</v>
+      </c>
+      <c r="F37" s="6">
+        <v>9</v>
+      </c>
+      <c r="G37" s="6">
+        <v>15</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I37" s="6">
+        <v>33</v>
+      </c>
+      <c r="J37" s="6">
+        <v>33</v>
+      </c>
       <c r="K37" s="5"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="10"/>
-      <c r="B38" s="3"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
+      <c r="A38" s="11">
+        <v>46123</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" s="6">
+        <v>10</v>
+      </c>
+      <c r="F38" s="6">
+        <v>8</v>
+      </c>
+      <c r="G38" s="6">
+        <v>18</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I38" s="6">
+        <v>42</v>
+      </c>
+      <c r="J38" s="6">
+        <v>40</v>
+      </c>
       <c r="K38" s="5"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="10"/>
-      <c r="B39" s="3"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="5"/>
+      <c r="A39" s="11">
+        <v>46123</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="6">
+        <v>9</v>
+      </c>
+      <c r="F39" s="6">
+        <v>9</v>
+      </c>
+      <c r="G39" s="6">
+        <v>20</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I39" s="6">
+        <v>45</v>
+      </c>
+      <c r="J39" s="6">
+        <v>48</v>
+      </c>
+      <c r="K39" s="5" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="10"/>
-      <c r="B40" s="3"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6"/>
-      <c r="J40" s="6"/>
+      <c r="A40" s="11">
+        <v>46123</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E40" s="6">
+        <v>9</v>
+      </c>
+      <c r="F40" s="6">
+        <v>7</v>
+      </c>
+      <c r="G40" s="6">
+        <v>12</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I40" s="6">
+        <v>33</v>
+      </c>
+      <c r="J40" s="6">
+        <v>37</v>
+      </c>
       <c r="K40" s="5"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="10"/>
-      <c r="B41" s="3"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="6"/>
-      <c r="J41" s="6"/>
+      <c r="A41" s="11">
+        <v>46123</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E41" s="6">
+        <v>8</v>
+      </c>
+      <c r="F41" s="6">
+        <v>10</v>
+      </c>
+      <c r="G41" s="6">
+        <v>19</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I41" s="6">
+        <v>45</v>
+      </c>
+      <c r="J41" s="6">
+        <v>41</v>
+      </c>
       <c r="K41" s="5"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="10"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="6"/>
+      <c r="A42" s="11">
+        <v>46123</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E42" s="6">
+        <v>9</v>
+      </c>
+      <c r="F42" s="6">
+        <v>9</v>
+      </c>
+      <c r="G42" s="6">
+        <v>13</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I42" s="6">
+        <v>32</v>
+      </c>
+      <c r="J42" s="6">
+        <v>41</v>
+      </c>
       <c r="K42" s="5"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="10"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="6"/>
+      <c r="A43" s="11">
+        <v>46123</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E43" s="6">
+        <v>8</v>
+      </c>
+      <c r="F43" s="6">
+        <v>7</v>
+      </c>
+      <c r="G43" s="6">
+        <v>14</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I43" s="6">
+        <v>40</v>
+      </c>
+      <c r="J43" s="6">
+        <v>47</v>
+      </c>
       <c r="K43" s="5"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" s="10"/>
-      <c r="B44" s="3"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="6"/>
+      <c r="A44" s="11">
+        <v>46123</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E44" s="6">
+        <v>9</v>
+      </c>
+      <c r="F44" s="6">
+        <v>9</v>
+      </c>
+      <c r="G44" s="6">
+        <v>12</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I44" s="6">
+        <v>42</v>
+      </c>
+      <c r="J44" s="6">
+        <v>32</v>
+      </c>
       <c r="K44" s="5"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="10"/>
-      <c r="B45" s="3"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="6"/>
-      <c r="J45" s="6"/>
+      <c r="A45" s="11">
+        <v>46123</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E45" s="6">
+        <v>6</v>
+      </c>
+      <c r="F45" s="6">
+        <v>10</v>
+      </c>
+      <c r="G45" s="6">
+        <v>12</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I45" s="6">
+        <v>42</v>
+      </c>
+      <c r="J45" s="6">
+        <v>42</v>
+      </c>
       <c r="K45" s="5"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" s="10"/>
-      <c r="B46" s="3"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="6"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="6"/>
+      <c r="A46" s="11">
+        <v>46123</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E46" s="6">
+        <v>7</v>
+      </c>
+      <c r="F46" s="6">
+        <v>9</v>
+      </c>
+      <c r="G46" s="6">
+        <v>9</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I46" s="6">
+        <v>32</v>
+      </c>
+      <c r="J46" s="6">
+        <v>39</v>
+      </c>
       <c r="K46" s="5"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="10"/>
-      <c r="B47" s="3"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="6"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="6"/>
+      <c r="A47" s="11">
+        <v>46123</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E47" s="6">
+        <v>6</v>
+      </c>
+      <c r="F47" s="6">
+        <v>9</v>
+      </c>
+      <c r="G47" s="6">
+        <v>15</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I47" s="6">
+        <v>33</v>
+      </c>
+      <c r="J47" s="6">
+        <v>33</v>
+      </c>
       <c r="K47" s="5"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" s="10"/>
-      <c r="B48" s="3"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="6"/>
+      <c r="A48" s="11">
+        <v>46123</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E48" s="6">
+        <v>10</v>
+      </c>
+      <c r="F48" s="6">
+        <v>8</v>
+      </c>
+      <c r="G48" s="6">
+        <v>18</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I48" s="6">
+        <v>42</v>
+      </c>
+      <c r="J48" s="6">
+        <v>40</v>
+      </c>
       <c r="K48" s="5"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A49" s="10"/>
-      <c r="B49" s="3"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="6"/>
-      <c r="J49" s="6"/>
-      <c r="K49" s="5"/>
+      <c r="A49" s="11">
+        <v>46123</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E49" s="6">
+        <v>9</v>
+      </c>
+      <c r="F49" s="6">
+        <v>9</v>
+      </c>
+      <c r="G49" s="6">
+        <v>20</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I49" s="6">
+        <v>45</v>
+      </c>
+      <c r="J49" s="6">
+        <v>48</v>
+      </c>
+      <c r="K49" s="5" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" s="10"/>
-      <c r="B50" s="3"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6"/>
-      <c r="J50" s="6"/>
+      <c r="A50" s="11">
+        <v>46123</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E50" s="6">
+        <v>9</v>
+      </c>
+      <c r="F50" s="6">
+        <v>7</v>
+      </c>
+      <c r="G50" s="6">
+        <v>12</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I50" s="6">
+        <v>33</v>
+      </c>
+      <c r="J50" s="6">
+        <v>37</v>
+      </c>
       <c r="K50" s="5"/>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" s="10"/>
-      <c r="B51" s="3"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="6"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="6"/>
-      <c r="J51" s="6"/>
-      <c r="K51" s="5"/>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A52" s="10"/>
-      <c r="B52" s="3"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="5"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="6"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="6"/>
-      <c r="J52" s="6"/>
-      <c r="K52" s="5"/>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A53" s="10"/>
-      <c r="B53" s="3"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="5"/>
-      <c r="E53" s="6"/>
-      <c r="F53" s="6"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="6"/>
-      <c r="K53" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
